--- a/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260803.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260803.xlsx
@@ -1085,17 +1085,17 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>2458</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>義隆</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>56,078,000</t>
+          <t>8,032,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1107,17 +1107,17 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>義隆</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>8,032,000</t>
+          <t>56,078,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>4766</t>
+          <t>2206</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>南寶</t>
+          <t>三陽工業</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>3,577,000</t>
+          <t>17,902,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1283,17 +1283,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2206</t>
+          <t>4766</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>三陽工業</t>
+          <t>南寶</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>17,902,000</t>
+          <t>3,577,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>17,001,000</t>
+          <t>2,181,678</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1327,17 +1327,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>2,181,678</t>
+          <t>17,001,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1503,17 +1503,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>智易</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>5,317,000</t>
+          <t>2,960,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1525,17 +1525,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>智易</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>2,960,000</t>
+          <t>5,317,000</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1591,17 +1591,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>2504</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>國產</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>24,799,000</t>
+          <t>7,825,000</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1613,17 +1613,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2504</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>國產</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>7,825,000</t>
+          <t>24,799,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
